--- a/data/trans_orig/Q47-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su talla</t>
+          <t>Población según su talla (tasa de respuesta: 98,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>175,4; 176,62</t>
+          <t>175,41; 176,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>175,22; 176,66</t>
+          <t>175,22; 176,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175,73; 177,1</t>
+          <t>175,74; 177,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175,0; 177,71</t>
+          <t>175,06; 177,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>162,76; 163,86</t>
+          <t>162,81; 163,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>162,72; 163,93</t>
+          <t>162,69; 163,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>162,79; 163,95</t>
+          <t>162,76; 163,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>162,52; 164,51</t>
+          <t>162,45; 164,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>169,25; 170,41</t>
+          <t>169,28; 170,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169,11; 170,39</t>
+          <t>169,18; 170,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169,42; 170,72</t>
+          <t>169,42; 170,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>169,64; 171,87</t>
+          <t>169,63; 171,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>175,27; 176,34</t>
+          <t>175,3; 176,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>175,58; 176,67</t>
+          <t>175,53; 176,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175,72; 176,99</t>
+          <t>175,75; 177,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174,88; 176,54</t>
+          <t>174,85; 176,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>163,02; 163,94</t>
+          <t>163,0; 164,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>163,12; 164,22</t>
+          <t>163,08; 164,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>163,33; 164,35</t>
+          <t>163,25; 164,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>159,2; 163,97</t>
+          <t>158,9; 163,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>169,64; 170,62</t>
+          <t>169,64; 170,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169,68; 170,79</t>
+          <t>169,71; 170,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169,67; 170,8</t>
+          <t>169,69; 170,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>164,65; 169,85</t>
+          <t>164,54; 169,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174,01; 175,0</t>
+          <t>173,95; 174,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>174,29; 175,38</t>
+          <t>174,24; 175,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174,93; 176,07</t>
+          <t>174,93; 176,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175,23; 176,48</t>
+          <t>175,29; 176,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>161,67; 162,66</t>
+          <t>161,69; 162,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>161,41; 162,4</t>
+          <t>161,37; 162,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>162,62; 163,64</t>
+          <t>162,6; 163,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>163,26; 164,14</t>
+          <t>163,28; 164,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167,59; 168,57</t>
+          <t>167,59; 168,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167,69; 168,71</t>
+          <t>167,75; 168,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168,86; 169,86</t>
+          <t>168,83; 169,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>169,26; 170,26</t>
+          <t>169,26; 170,25</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172,46; 173,73</t>
+          <t>172,49; 173,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172,24; 173,4</t>
+          <t>172,31; 173,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173,58; 174,83</t>
+          <t>173,6; 174,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174,35; 179,58</t>
+          <t>174,38; 179,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>159,92; 161,04</t>
+          <t>159,91; 160,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,25; 161,3</t>
+          <t>160,22; 161,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,53; 162,57</t>
+          <t>161,47; 162,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>161,84; 163,13</t>
+          <t>161,84; 163,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,17; 167,41</t>
+          <t>166,29; 167,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,22; 167,36</t>
+          <t>166,28; 167,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167,59; 168,67</t>
+          <t>167,55; 168,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>168,29; 175,35</t>
+          <t>168,3; 175,16</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>168,45; 169,91</t>
+          <t>168,48; 169,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>169,16; 170,34</t>
+          <t>169,14; 170,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170,84; 172,25</t>
+          <t>170,91; 172,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172,14; 173,14</t>
+          <t>172,14; 173,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>158,28; 159,48</t>
+          <t>158,29; 159,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>158,54; 159,69</t>
+          <t>158,52; 159,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>158,42; 159,59</t>
+          <t>158,41; 159,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>160,84; 161,65</t>
+          <t>160,84; 161,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>163,37; 164,6</t>
+          <t>163,33; 164,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163,74; 164,91</t>
+          <t>163,76; 164,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164,62; 165,87</t>
+          <t>164,56; 165,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>166,63; 167,5</t>
+          <t>166,55; 167,45</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167,55; 168,81</t>
+          <t>167,57; 168,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167,36; 168,94</t>
+          <t>167,28; 168,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>168,55; 170,01</t>
+          <t>168,6; 169,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169,27; 170,33</t>
+          <t>169,26; 170,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>156,91; 158,13</t>
+          <t>156,78; 158,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>157,69; 159,13</t>
+          <t>157,72; 159,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>157,9; 159,27</t>
+          <t>157,98; 159,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>156,27; 160,11</t>
+          <t>156,29; 160,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>161,85; 163,07</t>
+          <t>161,78; 162,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>162,44; 163,77</t>
+          <t>162,39; 163,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162,98; 164,32</t>
+          <t>163,02; 164,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>159,39; 164,86</t>
+          <t>158,65; 164,9</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>166,55; 168,22</t>
+          <t>166,38; 168,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>166,46; 168,46</t>
+          <t>166,61; 168,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167,44; 169,13</t>
+          <t>167,42; 169,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167,47; 168,72</t>
+          <t>167,47; 168,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>155,7; 157,36</t>
+          <t>155,68; 157,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>156,62; 158,08</t>
+          <t>156,71; 158,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>156,89; 158,46</t>
+          <t>156,82; 158,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>158,28; 159,08</t>
+          <t>158,25; 159,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>159,86; 161,33</t>
+          <t>159,85; 161,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160,94; 162,34</t>
+          <t>160,84; 162,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161,37; 162,79</t>
+          <t>161,31; 162,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>162,15; 163,07</t>
+          <t>162,13; 163,02</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,42</t>
+          <t>172,92; 173,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>172,87; 173,39</t>
+          <t>172,83; 173,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173,59; 174,13</t>
+          <t>173,58; 174,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173,64; 176,03</t>
+          <t>173,63; 176,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>160,65; 161,11</t>
+          <t>160,69; 161,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>160,78; 161,26</t>
+          <t>160,83; 161,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>161,22; 161,71</t>
+          <t>161,22; 161,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>160,25; 162,02</t>
+          <t>159,95; 162,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,18</t>
+          <t>166,72; 167,19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166,78; 167,24</t>
+          <t>166,79; 167,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>167,32; 167,8</t>
+          <t>167,32; 167,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>166,73; 169,32</t>
+          <t>166,77; 169,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q47-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q47-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176,28</t>
+          <t>176,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>163,54</t>
+          <t>163,35</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>170,7</t>
+          <t>170,09</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>175,41; 176,63</t>
+          <t>175,39; 176,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>175,22; 176,64</t>
+          <t>175,16; 176,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>175,74; 177,11</t>
+          <t>175,79; 177,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175,06; 177,73</t>
+          <t>174,99; 177,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>162,81; 163,9</t>
+          <t>162,75; 163,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>162,69; 163,86</t>
+          <t>162,71; 163,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>162,76; 163,96</t>
+          <t>162,81; 164,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>162,45; 164,55</t>
+          <t>162,38; 164,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>169,28; 170,41</t>
+          <t>169,29; 170,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169,18; 170,46</t>
+          <t>169,18; 170,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>169,42; 170,64</t>
+          <t>169,39; 170,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>169,63; 171,75</t>
+          <t>169,07; 171,12</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>175,63</t>
+          <t>175,49</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>162,3</t>
+          <t>163,68</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>168,36</t>
+          <t>169,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>175,3; 176,33</t>
+          <t>175,28; 176,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>175,53; 176,65</t>
+          <t>175,62; 176,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175,75; 177,03</t>
+          <t>175,76; 177,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174,85; 176,52</t>
+          <t>174,75; 176,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>163,0; 164,03</t>
+          <t>162,96; 164,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>163,08; 164,18</t>
+          <t>163,06; 164,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>163,25; 164,24</t>
+          <t>163,28; 164,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>158,9; 163,92</t>
+          <t>163,11; 164,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>169,64; 170,66</t>
+          <t>169,66; 170,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169,71; 170,81</t>
+          <t>169,75; 170,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169,69; 170,78</t>
+          <t>169,63; 170,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>164,54; 169,85</t>
+          <t>168,83; 170,13</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175,88</t>
+          <t>175,84</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>163,69</t>
+          <t>163,63</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>169,75</t>
+          <t>169,72</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>173,95; 174,96</t>
+          <t>174,03; 175,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>174,24; 175,3</t>
+          <t>174,31; 175,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>174,93; 176,04</t>
+          <t>174,9; 176,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175,29; 176,53</t>
+          <t>175,26; 176,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>161,69; 162,68</t>
+          <t>161,62; 162,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>161,37; 162,37</t>
+          <t>161,4; 162,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>162,6; 163,6</t>
+          <t>162,55; 163,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>163,28; 164,18</t>
+          <t>163,22; 164,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167,59; 168,55</t>
+          <t>167,65; 168,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167,75; 168,76</t>
+          <t>167,71; 168,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>168,83; 169,82</t>
+          <t>168,84; 169,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>169,26; 170,25</t>
+          <t>169,26; 170,22</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176,6</t>
+          <t>174,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>162,66</t>
+          <t>162,84</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>170,6</t>
+          <t>168,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>172,49; 173,73</t>
+          <t>172,5; 173,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>172,31; 173,4</t>
+          <t>172,29; 173,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173,6; 174,86</t>
+          <t>173,57; 174,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>174,38; 179,67</t>
+          <t>174,0; 175,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>159,91; 160,98</t>
+          <t>159,88; 161,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>160,22; 161,24</t>
+          <t>160,25; 161,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,47; 162,54</t>
+          <t>161,58; 162,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>161,84; 163,08</t>
+          <t>162,48; 163,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>166,29; 167,42</t>
+          <t>166,23; 167,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166,28; 167,3</t>
+          <t>166,22; 167,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167,55; 168,68</t>
+          <t>167,54; 168,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>168,3; 175,16</t>
+          <t>168,12; 168,99</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>172,64</t>
+          <t>172,74</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>161,26</t>
+          <t>161,36</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>167,03</t>
+          <t>167,06</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>168,48; 169,93</t>
+          <t>168,51; 169,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>169,14; 170,38</t>
+          <t>169,11; 170,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170,91; 172,24</t>
+          <t>170,86; 172,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172,14; 173,2</t>
+          <t>172,23; 173,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>158,29; 159,54</t>
+          <t>158,26; 159,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>158,52; 159,68</t>
+          <t>158,48; 159,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>158,41; 159,61</t>
+          <t>158,43; 159,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>160,84; 161,66</t>
+          <t>160,98; 161,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>163,33; 164,48</t>
+          <t>163,32; 164,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>163,76; 164,9</t>
+          <t>163,71; 164,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>164,56; 165,82</t>
+          <t>164,51; 165,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>166,55; 167,45</t>
+          <t>166,66; 167,49</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169,82</t>
+          <t>169,95</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>158,27</t>
+          <t>160,0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>162,63</t>
+          <t>164,82</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>167,57; 168,83</t>
+          <t>167,56; 168,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167,28; 168,85</t>
+          <t>167,31; 168,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>168,6; 169,99</t>
+          <t>168,59; 170,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169,26; 170,32</t>
+          <t>169,44; 170,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>156,78; 158,07</t>
+          <t>156,87; 158,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>157,72; 159,16</t>
+          <t>157,76; 159,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>157,98; 159,21</t>
+          <t>157,91; 159,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>156,29; 160,12</t>
+          <t>159,57; 160,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>161,78; 162,99</t>
+          <t>161,85; 163,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>162,39; 163,8</t>
+          <t>162,46; 163,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>163,02; 164,32</t>
+          <t>163,06; 164,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>158,65; 164,9</t>
+          <t>164,41; 165,27</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168,11</t>
+          <t>168,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>158,66</t>
+          <t>158,72</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>162,6</t>
+          <t>162,7</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>166,38; 168,14</t>
+          <t>166,45; 168,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>166,61; 168,66</t>
+          <t>166,62; 168,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167,42; 169,17</t>
+          <t>167,43; 169,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167,47; 168,76</t>
+          <t>167,67; 168,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>155,68; 157,25</t>
+          <t>155,65; 157,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>156,71; 158,17</t>
+          <t>156,68; 158,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>156,82; 158,41</t>
+          <t>156,84; 158,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>158,25; 159,13</t>
+          <t>158,27; 159,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>159,85; 161,39</t>
+          <t>159,92; 161,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160,84; 162,31</t>
+          <t>160,78; 162,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>161,31; 162,77</t>
+          <t>161,29; 162,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>162,13; 163,02</t>
+          <t>162,24; 163,18</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>174,31</t>
+          <t>173,71</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>161,47</t>
+          <t>162,1</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>167,79</t>
+          <t>167,78</t>
         </is>
       </c>
     </row>
@@ -1696,47 +1696,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>172,92; 173,44</t>
+          <t>172,91; 173,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>172,83; 173,39</t>
+          <t>172,85; 173,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173,58; 174,1</t>
+          <t>173,58; 174,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173,63; 176,17</t>
+          <t>173,47; 173,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>160,69; 161,12</t>
+          <t>160,66; 161,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>160,83; 161,28</t>
+          <t>160,78; 161,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>161,22; 161,69</t>
+          <t>161,21; 161,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>159,95; 162,0</t>
+          <t>161,91; 162,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>166,72; 167,19</t>
+          <t>166,73; 167,16</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>167,32; 167,79</t>
+          <t>167,28; 167,77</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>166,77; 169,25</t>
+          <t>167,54; 168,0</t>
         </is>
       </c>
     </row>
